--- a/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
+++ b/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0937B675-5506-4610-80AD-86AA53AB862B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329707D1-BCEE-4980-8C36-DC2501510F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5010" yWindow="6240" windowWidth="20925" windowHeight="8190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>البريد الإلكتروني</t>
   </si>
@@ -39,13 +39,7 @@
     <t>4. لا تُنشئ العملية مستخدمين جدد؛ يجب أن يكون مستخدم Firebase Auth موجودًا.</t>
   </si>
   <si>
-    <t>w-a-atwala@qz.org.sa</t>
-  </si>
-  <si>
-    <t>n-r-arbya@qz.org.sa</t>
-  </si>
-  <si>
-    <t>r-g-alfraj@qz.org.sa</t>
+    <t>math-science-sup@qz.org.sa</t>
   </si>
 </sst>
 </file>
@@ -526,34 +520,21 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2">
-        <v>1111478259</v>
+        <v>1088888888</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>1108811546</v>
-      </c>
+      <c r="A3" s="5"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>1110636832</v>
-      </c>
+      <c r="A4" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:B1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{A9FFD132-2395-41B9-8214-2CB3B6FD6C8B}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>

--- a/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
+++ b/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329707D1-BCEE-4980-8C36-DC2501510F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8426A86E-0F7C-454B-88FA-0B57FCD47032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5010" yWindow="6240" windowWidth="20925" windowHeight="8190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5160" yWindow="2865" windowWidth="9780" windowHeight="12045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="تحديث كلمات المرور" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>البريد الإلكتروني</t>
   </si>
@@ -39,7 +39,52 @@
     <t>4. لا تُنشئ العملية مستخدمين جدد؛ يجب أن يكون مستخدم Firebase Auth موجودًا.</t>
   </si>
   <si>
-    <t>math-science-sup@qz.org.sa</t>
+    <t>a.alhomidi@qz.org.sa</t>
+  </si>
+  <si>
+    <t>t.alamer@qz.org.sa</t>
+  </si>
+  <si>
+    <t>a.alfarag@qz.org.sa</t>
+  </si>
+  <si>
+    <t>ms.alswiket@qz.org.sa</t>
+  </si>
+  <si>
+    <t>s.alturiqe@qz.org.sa</t>
+  </si>
+  <si>
+    <t>h.aljower@qz.org.sa</t>
+  </si>
+  <si>
+    <t>s.alosaimi@qz.org.sa</t>
+  </si>
+  <si>
+    <t>aa.alnutifi@qz.org.sa</t>
+  </si>
+  <si>
+    <t>s.alnafea@qz.org.sa</t>
+  </si>
+  <si>
+    <t>s.alslman@qz.org.sa</t>
+  </si>
+  <si>
+    <t>n.alshammri@qz.org.sa</t>
+  </si>
+  <si>
+    <t>f.alzuwaid@qz.org.sa</t>
+  </si>
+  <si>
+    <t>n.alhamiyn@qz.org.sa</t>
+  </si>
+  <si>
+    <t>h.alshaya@qz.org.sa</t>
+  </si>
+  <si>
+    <t>mm.almousa@qz.org.sa</t>
+  </si>
+  <si>
+    <t>L.altayar@qz.org.sa</t>
   </si>
 </sst>
 </file>
@@ -77,8 +122,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="Tajawal"/>
     </font>
   </fonts>
   <fills count="5">
@@ -100,8 +144,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -138,13 +182,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
       </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -152,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -163,8 +211,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -504,14 +553,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -519,22 +568,139 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B2">
-        <v>1088888888</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
+        <v>1064887043</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1089814881</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>1082597996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>1066188374</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>1059320620</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>1090509850</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
+        <v>1109500403</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>1012769046</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <v>1064636127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <v>1090757889</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
+        <v>1026235844</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <v>1085493300</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>1067471167</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15">
+        <v>1088778129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16">
+        <v>1057720870</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17">
+        <v>110607075</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <hyperlinks>
+    <hyperlink ref="A10" r:id="rId1" xr:uid="{B37C0921-7156-490D-93D7-5719BB80EFDE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>

--- a/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
+++ b/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8426A86E-0F7C-454B-88FA-0B57FCD47032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D19467-C774-479F-9FCD-751D5C49FBB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5160" yWindow="2865" windowWidth="9780" windowHeight="12045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="3585" windowWidth="9960" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="تحديث كلمات المرور" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>البريد الإلكتروني</t>
   </si>
@@ -39,52 +39,22 @@
     <t>4. لا تُنشئ العملية مستخدمين جدد؛ يجب أن يكون مستخدم Firebase Auth موجودًا.</t>
   </si>
   <si>
-    <t>a.alhomidi@qz.org.sa</t>
-  </si>
-  <si>
-    <t>t.alamer@qz.org.sa</t>
-  </si>
-  <si>
-    <t>a.alfarag@qz.org.sa</t>
-  </si>
-  <si>
-    <t>ms.alswiket@qz.org.sa</t>
-  </si>
-  <si>
-    <t>s.alturiqe@qz.org.sa</t>
-  </si>
-  <si>
-    <t>h.aljower@qz.org.sa</t>
-  </si>
-  <si>
-    <t>s.alosaimi@qz.org.sa</t>
-  </si>
-  <si>
-    <t>aa.alnutifi@qz.org.sa</t>
-  </si>
-  <si>
-    <t>s.alnafea@qz.org.sa</t>
-  </si>
-  <si>
-    <t>s.alslman@qz.org.sa</t>
-  </si>
-  <si>
-    <t>n.alshammri@qz.org.sa</t>
-  </si>
-  <si>
-    <t>f.alzuwaid@qz.org.sa</t>
-  </si>
-  <si>
-    <t>n.alhamiyn@qz.org.sa</t>
-  </si>
-  <si>
-    <t>h.alshaya@qz.org.sa</t>
-  </si>
-  <si>
-    <t>mm.almousa@qz.org.sa</t>
-  </si>
-  <si>
-    <t>L.altayar@qz.org.sa</t>
+    <t>n.albader@qz.org.sa</t>
+  </si>
+  <si>
+    <t>f.alobawe@qz.org.sa</t>
+  </si>
+  <si>
+    <t>sarah@qz.org.sa</t>
+  </si>
+  <si>
+    <t>aa.almansor@qz.org.sa</t>
+  </si>
+  <si>
+    <t>hanaz@qz.org.sa</t>
+  </si>
+  <si>
+    <t>ny.almasoud@qz.org.sa</t>
   </si>
 </sst>
 </file>
@@ -200,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -214,6 +184,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -553,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -568,12 +539,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2">
-        <v>1064887043</v>
+      <c r="B2" s="5">
+        <v>1037656246</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -581,7 +552,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>1089814881</v>
+        <v>1031179292</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -589,7 +560,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>1082597996</v>
+        <v>1057573352</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -597,7 +568,7 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>1066188374</v>
+        <v>1092680873</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -605,7 +576,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>1059320620</v>
+        <v>1059044766</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -613,94 +584,38 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>1090509850</v>
+        <v>1042991818</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8">
-        <v>1109500403</v>
-      </c>
+      <c r="A8" s="4"/>
     </row>
     <row r="9" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9">
-        <v>1012769046</v>
-      </c>
+      <c r="A9" s="4"/>
     </row>
     <row r="10" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10">
-        <v>1064636127</v>
-      </c>
+      <c r="A10" s="4"/>
     </row>
     <row r="11" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11">
-        <v>1090757889</v>
-      </c>
+      <c r="A11" s="4"/>
     </row>
     <row r="12" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12">
-        <v>1026235844</v>
-      </c>
+      <c r="A12" s="4"/>
     </row>
     <row r="13" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13">
-        <v>1085493300</v>
-      </c>
+      <c r="A13" s="4"/>
     </row>
     <row r="14" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14">
-        <v>1067471167</v>
-      </c>
+      <c r="A14" s="4"/>
     </row>
     <row r="15" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15">
-        <v>1088778129</v>
-      </c>
+      <c r="A15" s="4"/>
     </row>
     <row r="16" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16">
-        <v>1057720870</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17">
-        <v>110607075</v>
-      </c>
+      <c r="A16" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:B1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <hyperlinks>
-    <hyperlink ref="A10" r:id="rId1" xr:uid="{B37C0921-7156-490D-93D7-5719BB80EFDE}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>

--- a/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
+++ b/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D19467-C774-479F-9FCD-751D5C49FBB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15397248-1C4E-4F37-9AAC-2CC8A294DE1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="3585" windowWidth="9960" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="تحديث كلمات المرور" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>البريد الإلكتروني</t>
   </si>
@@ -39,22 +39,7 @@
     <t>4. لا تُنشئ العملية مستخدمين جدد؛ يجب أن يكون مستخدم Firebase Auth موجودًا.</t>
   </si>
   <si>
-    <t>n.albader@qz.org.sa</t>
-  </si>
-  <si>
-    <t>f.alobawe@qz.org.sa</t>
-  </si>
-  <si>
-    <t>sarah@qz.org.sa</t>
-  </si>
-  <si>
-    <t>aa.almansor@qz.org.sa</t>
-  </si>
-  <si>
-    <t>hanaz@qz.org.sa</t>
-  </si>
-  <si>
-    <t>ny.almasoud@qz.org.sa</t>
+    <t>riadah3@qz.org.sa</t>
   </si>
 </sst>
 </file>
@@ -529,9 +514,10 @@
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="4" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -539,53 +525,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5">
-        <v>1037656246</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>1031179292</v>
-      </c>
+      <c r="B2">
+        <v>1022222222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
     </row>
     <row r="4" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>1057573352</v>
-      </c>
+      <c r="A4" s="4"/>
     </row>
     <row r="5" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5">
-        <v>1092680873</v>
-      </c>
+      <c r="A5" s="4"/>
     </row>
     <row r="6" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6">
-        <v>1059044766</v>
-      </c>
+      <c r="A6" s="4"/>
     </row>
     <row r="7" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>1042991818</v>
-      </c>
+      <c r="A7" s="4"/>
     </row>
     <row r="8" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>

--- a/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
+++ b/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15397248-1C4E-4F37-9AAC-2CC8A294DE1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADDFA3C-A2D2-42E8-A432-BCCD3587282F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="15645" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="تحديث كلمات المرور" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
     <t>4. لا تُنشئ العملية مستخدمين جدد؛ يجب أن يكون مستخدم Firebase Auth موجودًا.</t>
   </si>
   <si>
-    <t>riadah3@qz.org.sa</t>
+    <t>m-f-elfahd@qz.org.sa</t>
   </si>
 </sst>
 </file>
@@ -509,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -525,17 +525,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2">
-        <v>1022222222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
+      <c r="B2" s="5">
+        <v>1092685119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
     </row>
     <row r="4" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
@@ -572,9 +571,6 @@
     </row>
     <row r="15" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
-    </row>
-    <row r="16" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:B1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
